--- a/resources/tools/wordlist_E-J/lessons/lesson-12.xlsx
+++ b/resources/tools/wordlist_E-J/lessons/lesson-12.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B138"/>
+  <dimension ref="A1:B139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,120 +431,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>leg; foot</t>
+          <t>stomach</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>足|あし</t>
+          <t>おなか</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>meaning</t>
+          <t>leg; foot</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>意味|いみ</t>
+          <t>足|あし</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>restroom</t>
+          <t>throat</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>お手洗い|おてあらい</t>
+          <t>のど</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>stomach</t>
+          <t>tooth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>おなか</t>
+          <t>歯|は</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cold</t>
+          <t>influenza; flu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>風邪|かぜ</t>
+          <t>インフルエンザ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>girlfriend</t>
+          <t>cold</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>彼女|かのじょ</t>
+          <t>風邪|かぜ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>boyfriend</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>彼|かれ</t>
+          <t>せき</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>temperature (weather)</t>
+          <t>hangover</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>気温|きおん</t>
+          <t>二日酔い|ふつかよい</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cloudy weather</t>
+          <t>homesickness</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>曇り|くもり</t>
+          <t>ホームシック</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>match; game</t>
+          <t>allergy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>試合|しあい</t>
+          <t>アレルギー</t>
         </is>
       </c>
     </row>
@@ -563,252 +563,252 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>politics</t>
+          <t>egg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>政治|せいじ</t>
+          <t>卵|たまご</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>grade (on a test, etc.)</t>
+          <t>clothes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>成績|せいせき</t>
+          <t>服|ふく</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cough</t>
+          <t>thing (concrete object)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>せき</t>
+          <t>物|もの</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>throat</t>
+          <t>present</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>のど</t>
+          <t>プレゼント</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tooth</t>
+          <t>train ticket; ticket</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>歯|は</t>
+          <t>切符|きっぷ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>charge; fee</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>花|はな</t>
+          <t>～代|～だい</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sunny weather</t>
+          <t>business to take care of</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>晴れ|はれ</t>
+          <t>用事|ようじ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>clothes</t>
+          <t>restroom</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>服|ふく</t>
+          <t>お手洗い|おてあらい</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hangover</t>
+          <t>match; game</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>二日酔い|ふつかよい</t>
+          <t>試合|しあい</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>politics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>プレゼント</t>
+          <t>政治|せいじ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>homesickness</t>
+          <t>grade (on a test, etc.)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ホームシック</t>
+          <t>成績|せいせき</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>minus</t>
+          <t>she; girlfriend</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>彼女|かのじょ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>thing (concrete object)</t>
+          <t>he; boyfriend</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>物|もの</t>
+          <t>彼|かれ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>boyfriend</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>雪|ゆき</t>
+          <t>彼氏|かれし</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>business to take care of</t>
+          <t>meaning</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>用事|ようじ</t>
+          <t>意味|いみ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sweet</t>
+          <t>narrow; not spacious</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>甘い|あまい</t>
+          <t>狭い|せまい</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hurt; painful</t>
+          <t>wide; spacious</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>痛い|いたい</t>
+          <t>広い|ひろい</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>there are many</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>多い|おおい</t>
+          <t>悪い|わるい</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>narrow; not spacious</t>
+          <t>hurt; painful</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>狭い|せまい</t>
+          <t>痛い|いたい</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>inconvenient; to have a scheduling conflict</t>
+          <t>sweet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>都合が悪い|つごうがわるい</t>
+          <t>甘い|あまい</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>there are many</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>悪い|わるい</t>
+          <t>多い|おおい</t>
         </is>
       </c>
     </row>
@@ -851,132 +851,132 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>to be interested (in...)</t>
+          <t>to have a fever</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>興味がある|きょうみがある</t>
+          <t>熱がある|ねつがある</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>to lose</t>
+          <t>to become thirsty</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>なくす</t>
+          <t>のどが渇く|のどがかわく</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>to have a fever</t>
+          <t>to pay (～を)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>熱がある|ねつがある</t>
+          <t>払う|はらう</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>to become thirsty</t>
+          <t>to lose (～を)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>のどが渇く|のどがかわく</t>
+          <t>なくす</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>to cough</t>
+          <t>to be interested (in...) (topic に)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>せきが出る|せきがでる</t>
+          <t>興味がある|きょうみがある</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>to break up; to separate</t>
+          <t>to cough</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>別れる|わかれる</t>
+          <t>せきが出る|せきがでる</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>to get nervous</t>
+          <t>to break up; to separate (person と)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>緊張する|きんちょうする</t>
+          <t>別れる|わかれる</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>to worry</t>
+          <t>to get nervous</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>心配する|しんぱいする</t>
+          <t>緊張する|きんちょうする</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Get well soon.</t>
+          <t>to worry</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>お大事に|おだいじに</t>
+          <t>心配する|しんぱいする</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>don't look well</t>
+          <t>Get well soon.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>元気がない|げんきがない</t>
+          <t>お大事に|おだいじに</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>probably; maybe</t>
+          <t>don't look well</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>多分|たぶん</t>
+          <t>元気がない|げんきがない</t>
         </is>
       </c>
     </row>
@@ -995,72 +995,72 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>probably; ..., right?</t>
+          <t>probably; maybe</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>～でしょう</t>
+          <t>多分|たぶん</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>degrees (temperature)</t>
+          <t>very soon; in a few moments/days</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>～度|～ど</t>
+          <t>もうすぐ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>for two to three days</t>
+          <t>for the first time</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>二三日|にさんにち</t>
+          <t>初めて|はじめて</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>because...</t>
+          <t>for two to three days</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>～ので</t>
+          <t>二三日|にさんにち</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>for the first time</t>
+          <t>moreover...</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>初めて|はじめて</t>
+          <t>それに</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>very soon; in a few moments/days</t>
+          <t>same</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>もうすぐ</t>
+          <t>同じ|おなじ</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>足の骨を折りました。|あしのほねをおりました。</t>
+          <t>足を骨折しました。|あしをこっせつしました。</t>
         </is>
       </c>
     </row>
@@ -1415,658 +1415,670 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>old times</t>
+          <t>intravenous feeding</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>昔|むかし</t>
+          <t>点滴|てんてき</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>old tale</t>
+          <t>old times</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>昔話|むかしばなし</t>
+          <t>昔|むかし</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ancient times</t>
+          <t>old tale</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>大昔|おおむかし</t>
+          <t>昔話|むかしばなし</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>once upon a time</t>
+          <t>ancient times</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>昔々|むかしむかし</t>
+          <t>大昔|おおむかし</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>people</t>
+          <t>once upon a time</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>人々|ひとびと</t>
+          <t>昔々|むかしむかし</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>people</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>時々|ときどき</t>
+          <t>人々|ひとびと</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>various</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>色々な|いろいろな</t>
+          <t>時々|ときどき</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>God</t>
+          <t>various</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>神さま|かみさま</t>
+          <t>色々な|いろいろな</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>shrine</t>
+          <t>God</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>神社|じんじゃ</t>
+          <t>神さま|かみさま</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Shinto religion</t>
+          <t>shrine</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>神道|しんとう</t>
+          <t>神社|じんじゃ</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Kobe City</t>
+          <t>Shinto</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>神戸市|こうべし</t>
+          <t>神道|しんとう</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>early</t>
+          <t>Kobe City</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>早い|はやい</t>
+          <t>神戸市|こうべし</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>to get up early</t>
+          <t>early</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>早起きする|はやおきする</t>
+          <t>早い|はやい</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>early morning</t>
+          <t>to get up early</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>早朝|そうちょう</t>
+          <t>早起きする|はやおきする</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>to get up</t>
+          <t>early morning</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>起きる|おきる</t>
+          <t>早朝|そうちょう</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>to wake someone up</t>
+          <t>to get up</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>起こす|おこす</t>
+          <t>起きる|おきる</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>to stand up</t>
+          <t>to wake someone up</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>起立する|きりつする</t>
+          <t>起こす|おこす</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>cow</t>
+          <t>reboot</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>牛|うし</t>
+          <t>再起動|さいきどう</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>milk</t>
+          <t>cow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>牛乳|ぎゅうにゅう</t>
+          <t>牛|うし</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>beef</t>
+          <t>milk</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>牛肉|ぎゅうにく</t>
+          <t>牛乳|ぎゅうにゅう</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>calf; veal</t>
+          <t>beef</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>子牛|こうし</t>
+          <t>牛肉|ぎゅうにく</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>to use</t>
+          <t>calf; veal</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>使う|つかう</t>
+          <t>子牛|こうし</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ambassador</t>
+          <t>to use</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>大使|たいし</t>
+          <t>使う|つかう</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>"Occupied"</t>
+          <t>ambassador</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>使用中|しようちゅう</t>
+          <t>大使|たいし</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>errand</t>
+          <t>"Occupied"</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>お使い|おつかい</t>
+          <t>使用中|しようちゅう</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>to work</t>
+          <t>errand</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>働く|はたらく</t>
+          <t>お使い|おつかい</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>both husband and wife working</t>
+          <t>to work</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>共働き|ともばたらき</t>
+          <t>働く|はたらく</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>both husband and wife working</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>労働|ろうどう</t>
+          <t>共働き|ともばたらき</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>to bring (a person) back</t>
+          <t>labor</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>連れて帰る|つれてかえる</t>
+          <t>労働|ろうどう</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>United Nations</t>
+          <t>to bring (a person) back</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>国連|こくれん</t>
+          <t>連れて帰る|つれてかえる</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>consecutive holidays</t>
+          <t>United Nations</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>連休|れんきゅう</t>
+          <t>国連|こくれん</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>to separate</t>
+          <t>consecutive holidays</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>別れる|わかれる</t>
+          <t>連休|れんきゅう</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>not in particular</t>
+          <t>to separate</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>別に|べつに</t>
+          <t>別れる|わかれる</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>special</t>
+          <t>not in particular</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>特別な|とくべつな</t>
+          <t>別に|べつに</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>discrimination</t>
+          <t>special</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>差別|さべつ</t>
+          <t>特別な|とくべつな</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>separately</t>
+          <t>discrimination</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>別々に|べつべつに</t>
+          <t>差別|さべつ</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>once</t>
+          <t>separately</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>一度|いちど</t>
+          <t>別々に|べつべつに</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>near future</t>
+          <t>once</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>今度|こんど</t>
+          <t>一度|いちど</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>temperature</t>
+          <t>near future</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>温度|おんど</t>
+          <t>今度|こんど</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>30 degrees</t>
+          <t>temperature</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>三十度|さんじゅうど</t>
+          <t>温度|おんど</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>attitude</t>
+          <t>30 degrees</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>態度|たいど</t>
+          <t>三十度|さんじゅうど</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>red color</t>
+          <t>attitude</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>赤|あか</t>
+          <t>態度|たいど</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>red color</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>赤い|あかい</t>
+          <t>赤|あか</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>baby</t>
+          <t>red</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>赤ちゃん|あかちゃん</t>
+          <t>赤い|あかい</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>the equator</t>
+          <t>baby</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>赤道|せきどう</t>
+          <t>赤ちゃん|あかちゃん</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>the Red Cross</t>
+          <t>the equator</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>赤十字|せきじゅうじ</t>
+          <t>赤道|せきどう</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>blue color</t>
+          <t>the Red Cross</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>青|あお</t>
+          <t>赤十字|せきじゅうじ</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>blue color</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>青い|あおい</t>
+          <t>青|あお</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>youth</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>青年|せいねん</t>
+          <t>青い|あおい</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>blue sky</t>
+          <t>youth</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>青空|あおぞら</t>
+          <t>青年|せいねん</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>green light</t>
+          <t>blue sky</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>青信号|あおしんごう</t>
+          <t>青空|あおぞら</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>green light</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>色|いろ</t>
+          <t>青信号|あおしんごう</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>various</t>
+          <t>color</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>色々な|いろいろな</t>
+          <t>色|いろ</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>scenery</t>
+          <t>various</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>景色|けしき</t>
+          <t>色々な|いろいろな</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>scenery</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>景色|けしき</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
           <t>characteristic</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>特色|とくしょく</t>
         </is>
